--- a/StructureDefinition-nimodipine-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-nimodipine-medicationAdministration-profile.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T11:15:53+00:00</t>
+    <t>2026-05-08T09:03:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-nimodipine-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-nimodipine-medicationAdministration-profile.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1885" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1886" uniqueCount="394">
   <si>
     <t>Property</t>
   </si>
@@ -51,16 +51,19 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T09:03:17+00:00</t>
+    <t>2026-05-08T09:31:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>MedicationAdministration profile for nimodipine in subarachnoid hemorrhage pathway.</t>
+    <t>MedicationAdministration profile for nimodipine in the subarachnoid hemorrhage pathway.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -118,9 +121,6 @@
   </si>
   <si>
     <t>Abstract</t>
-  </si>
-  <si>
-    <t>false</t>
   </si>
   <si>
     <t>Derivation</t>
@@ -569,7 +569,7 @@
 </t>
   </si>
   <si>
-    <t>Part of referenced event</t>
+    <t>Procedure this administration supports</t>
   </si>
   <si>
     <t>A larger event of which this particular event is a component or step.</t>
@@ -587,7 +587,7 @@
     <t>MedicationAdministration.status</t>
   </si>
   <si>
-    <t>in-progress | not-done | on-hold | completed | entered-in-error | stopped | unknown</t>
+    <t>Medication administration status</t>
   </si>
   <si>
     <t>Will generally be set to show that the administration has been completed.  For some long running administrations such as infusions, it is possible for an administration to be started but not completed or it may be paused while some other process is under way.</t>
@@ -621,7 +621,7 @@
 </t>
   </si>
   <si>
-    <t>Reason administration not performed</t>
+    <t>Reason medication was not given or status rationale</t>
   </si>
   <si>
     <t>A code indicating why the administration was not performed.</t>
@@ -670,7 +670,7 @@
 </t>
   </si>
   <si>
-    <t>What was administered</t>
+    <t>Administered medication</t>
   </si>
   <si>
     <t>Identifies the medication that was administered. This is either a link to a resource representing the details of the medication or a simple attribute carrying a code that identifies the medication from a known list of medications.</t>
@@ -772,10 +772,10 @@
 </t>
   </si>
   <si>
-    <t>Who received medication</t>
-  </si>
-  <si>
-    <t>The person or animal or group receiving the medication.</t>
+    <t>RES-Q registry patient</t>
+  </si>
+  <si>
+    <t>Patient who experienced the index stroke episode represented in this registry dataset.</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -797,10 +797,10 @@
 </t>
   </si>
   <si>
-    <t>Encounter administered as part of</t>
-  </si>
-  <si>
-    <t>The visit, admission, or other contact between patient and health care provider during which the medication administration was performed.</t>
+    <t>Index stroke encounter</t>
+  </si>
+  <si>
+    <t>Encounter that anchors the clinical fact to the acute stroke episode and hospital pathway.</t>
   </si>
   <si>
     <t>Event.encounter</t>
@@ -838,7 +838,7 @@
 </t>
   </si>
   <si>
-    <t>Specific date/time or interval of time during which the administration took place (or did not take place)</t>
+    <t>Administration date/time</t>
   </si>
   <si>
     <t>A specific date/time or interval of time during which the administration took place (or did not take place). For many administrations, such as swallowing a tablet the use of dateTime is more appropriate.</t>
@@ -995,7 +995,7 @@
 </t>
   </si>
   <si>
-    <t>Concept, condition or observation that supports why the medication was administered</t>
+    <t>Reason or clinical trigger for administration</t>
   </si>
   <si>
     <t>A code, Condition or observation that supports why the medication was administered.</t>
@@ -1082,7 +1082,7 @@
     <t>MedicationAdministration.dosage</t>
   </si>
   <si>
-    <t>Details of how medication was taken</t>
+    <t>Dose details</t>
   </si>
   <si>
     <t>Describes the medication dosage information details e.g. dose, rate, site, route, etc.</t>
@@ -1459,98 +1459,100 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
@@ -1736,10 +1738,10 @@
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
@@ -1819,7 +1821,7 @@
         <v>77</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG2" t="s" s="2">
         <v>78</v>

--- a/StructureDefinition-nimodipine-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-nimodipine-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T09:31:23+00:00</t>
+    <t>2026-05-08T10:13:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-nimodipine-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-nimodipine-medicationAdministration-profile.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1886" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1886" uniqueCount="395">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T10:13:17+00:00</t>
+    <t>2026-05-11T15:54:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -834,29 +834,33 @@
     <t>MedicationAdministration.occurence[x]</t>
   </si>
   <si>
+    <t>dateTime
+Period</t>
+  </si>
+  <si>
+    <t>Administration date/time</t>
+  </si>
+  <si>
+    <t>A specific date/time or interval of time during which the administration took place (or did not take place). For many administrations, such as swallowing a tablet the use of dateTime is more appropriate.</t>
+  </si>
+  <si>
+    <t>Event.occurrence[x]</t>
+  </si>
+  <si>
+    <t>FiveWs.done[x]</t>
+  </si>
+  <si>
+    <t>.effectiveTime</t>
+  </si>
+  <si>
+    <t>RXA-3 Date/Time Start of Administration / RXA-4 Date/Time End of Administration</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.recorded</t>
+  </si>
+  <si>
     <t xml:space="preserve">dateTime
 </t>
-  </si>
-  <si>
-    <t>Administration date/time</t>
-  </si>
-  <si>
-    <t>A specific date/time or interval of time during which the administration took place (or did not take place). For many administrations, such as swallowing a tablet the use of dateTime is more appropriate.</t>
-  </si>
-  <si>
-    <t>Event.occurrence[x]</t>
-  </si>
-  <si>
-    <t>FiveWs.done[x]</t>
-  </si>
-  <si>
-    <t>.effectiveTime</t>
-  </si>
-  <si>
-    <t>RXA-3 Date/Time Start of Administration / RXA-4 Date/Time End of Administration</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.recorded</t>
   </si>
   <si>
     <t>When the MedicationAdministration was first captured in the subject's record</t>
@@ -4812,13 +4816,13 @@
         <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4887,10 +4891,10 @@
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>77</v>
@@ -4898,10 +4902,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4924,13 +4928,13 @@
         <v>77</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4981,7 +4985,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5010,10 +5014,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5039,10 +5043,10 @@
         <v>192</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5073,7 +5077,7 @@
       </c>
       <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>77</v>
@@ -5091,7 +5095,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5120,10 +5124,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5146,13 +5150,13 @@
         <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5203,7 +5207,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5218,24 +5222,24 @@
         <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5258,7 +5262,7 @@
         <v>77</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L33" t="s" s="2">
         <v>218</v>
@@ -5344,10 +5348,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5458,14 +5462,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5487,10 +5491,10 @@
         <v>135</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>158</v>
@@ -5545,7 +5549,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5574,10 +5578,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5603,10 +5607,10 @@
         <v>192</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5636,10 +5640,10 @@
         <v>203</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>77</v>
@@ -5657,7 +5661,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5672,13 +5676,13 @@
         <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>77</v>
@@ -5686,10 +5690,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5712,13 +5716,13 @@
         <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5769,7 +5773,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>88</v>
@@ -5784,13 +5788,13 @@
         <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>77</v>
@@ -5798,10 +5802,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5824,13 +5828,13 @@
         <v>77</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5860,10 +5864,10 @@
         <v>203</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>77</v>
@@ -5881,7 +5885,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5896,24 +5900,24 @@
         <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5936,16 +5940,16 @@
         <v>77</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5995,7 +5999,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6010,24 +6014,24 @@
         <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6050,13 +6054,13 @@
         <v>77</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6107,7 +6111,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6128,18 +6132,18 @@
         <v>77</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6162,13 +6166,13 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6219,7 +6223,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6234,13 +6238,13 @@
         <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>77</v>
@@ -6248,10 +6252,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6274,13 +6278,13 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6331,7 +6335,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6343,7 +6347,7 @@
         <v>77</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>77</v>
@@ -6352,7 +6356,7 @@
         <v>77</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>77</v>
@@ -6360,10 +6364,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6386,7 +6390,7 @@
         <v>77</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L43" t="s" s="2">
         <v>218</v>
@@ -6472,10 +6476,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6586,14 +6590,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6615,10 +6619,10 @@
         <v>135</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>158</v>
@@ -6673,7 +6677,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6702,10 +6706,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6728,13 +6732,13 @@
         <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6785,7 +6789,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6794,7 +6798,7 @@
         <v>88</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>100</v>
@@ -6806,7 +6810,7 @@
         <v>77</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>77</v>
@@ -6814,10 +6818,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6843,13 +6847,13 @@
         <v>192</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6878,10 +6882,10 @@
         <v>203</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>77</v>
@@ -6899,7 +6903,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -6920,18 +6924,18 @@
         <v>77</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6957,10 +6961,10 @@
         <v>192</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6990,10 +6994,10 @@
         <v>203</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>77</v>
@@ -7011,7 +7015,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7032,18 +7036,18 @@
         <v>77</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7069,13 +7073,13 @@
         <v>192</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7104,10 +7108,10 @@
         <v>203</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>77</v>
@@ -7125,7 +7129,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7146,18 +7150,18 @@
         <v>77</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7180,16 +7184,16 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7239,7 +7243,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7248,7 +7252,7 @@
         <v>88</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>100</v>
@@ -7260,18 +7264,18 @@
         <v>77</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7294,16 +7298,16 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7353,7 +7357,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7362,7 +7366,7 @@
         <v>88</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>100</v>
@@ -7374,18 +7378,18 @@
         <v>77</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7408,16 +7412,16 @@
         <v>77</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7467,7 +7471,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7488,7 +7492,7 @@
         <v>77</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>77</v>

--- a/StructureDefinition-nimodipine-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-nimodipine-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:54:34+00:00</t>
+    <t>2026-05-11T15:54:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-nimodipine-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-nimodipine-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:54:44+00:00</t>
+    <t>2026-05-12T07:59:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-nimodipine-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-nimodipine-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T07:59:38+00:00</t>
+    <t>2026-05-12T09:41:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-nimodipine-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-nimodipine-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T09:41:56+00:00</t>
+    <t>2026-05-12T11:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-nimodipine-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-nimodipine-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T11:55:23+00:00</t>
+    <t>2026-05-13T14:14:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-nimodipine-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-nimodipine-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:14:43+00:00</t>
+    <t>2026-05-13T15:23:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-nimodipine-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-nimodipine-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T15:23:44+00:00</t>
+    <t>2026-05-14T08:09:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-nimodipine-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-nimodipine-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:09:55+00:00</t>
+    <t>2026-05-14T08:55:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-nimodipine-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-nimodipine-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:55:50+00:00</t>
+    <t>2026-05-14T09:35:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-nimodipine-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-nimodipine-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T09:35:04+00:00</t>
+    <t>2026-05-14T11:02:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-nimodipine-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-nimodipine-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T11:02:20+00:00</t>
+    <t>2026-05-15T10:10:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-nimodipine-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-nimodipine-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T10:10:20+00:00</t>
+    <t>2026-06-01T07:47:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-nimodipine-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-nimodipine-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T07:47:29+00:00</t>
+    <t>2026-06-01T10:24:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-nimodipine-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-nimodipine-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T10:24:12+00:00</t>
+    <t>2026-06-01T10:42:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-nimodipine-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-nimodipine-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T10:42:50+00:00</t>
+    <t>2026-06-01T12:57:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-nimodipine-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-nimodipine-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T12:57:35+00:00</t>
+    <t>2026-06-02T10:42:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-nimodipine-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-nimodipine-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T10:42:43+00:00</t>
+    <t>2026-06-03T07:55:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-nimodipine-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-nimodipine-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T07:55:03+00:00</t>
+    <t>2026-06-03T14:48:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-nimodipine-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-nimodipine-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T14:48:08+00:00</t>
+    <t>2026-06-03T14:50:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-nimodipine-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-nimodipine-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T14:50:23+00:00</t>
+    <t>2026-06-08T09:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-nimodipine-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-nimodipine-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T09:55:23+00:00</t>
+    <t>2026-06-08T10:51:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-nimodipine-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-nimodipine-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T10:51:55+00:00</t>
+    <t>2026-06-08T11:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
